--- a/data/trans_orig/AIRE_1_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/AIRE_1_R-Estudios-trans_orig.xlsx
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>19414</t>
+          <t>19505</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>26533</t>
+          <t>26653</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>68,38%</t>
+          <t>68,7%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>93,46%</t>
+          <t>93,88%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>21838</t>
+          <t>22568</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>31080</t>
+          <t>31231</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>66,07%</t>
+          <t>68,28%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>94,03%</t>
+          <t>94,49%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>45481</t>
+          <t>45420</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>56165</t>
+          <t>56317</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>74,02%</t>
+          <t>73,92%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>91,41%</t>
+          <t>91,66%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1858</t>
+          <t>1738</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8977</t>
+          <t>8886</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>31,62%</t>
+          <t>31,3%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1972</t>
+          <t>1821</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>11214</t>
+          <t>10484</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>33,93%</t>
+          <t>31,72%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>5278</t>
+          <t>5126</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>15962</t>
+          <t>16023</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>25,98%</t>
+          <t>26,08%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>163067</t>
+          <t>163444</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>190338</t>
+          <t>188495</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>75,25%</t>
+          <t>75,43%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>87,84%</t>
+          <t>86,99%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>172257</t>
+          <t>173960</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>202586</t>
+          <t>203403</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>66,71%</t>
+          <t>67,37%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>78,45%</t>
+          <t>78,77%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>345744</t>
+          <t>343213</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>388927</t>
+          <t>387791</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>72,8%</t>
+          <t>72,27%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>81,89%</t>
+          <t>81,65%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>26356</t>
+          <t>28199</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>53627</t>
+          <t>53250</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>24,75%</t>
+          <t>24,57%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>55644</t>
+          <t>54827</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>85973</t>
+          <t>84270</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>21,55%</t>
+          <t>21,23%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>33,29%</t>
+          <t>32,63%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>85996</t>
+          <t>87132</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>129179</t>
+          <t>131710</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>18,35%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>27,2%</t>
+          <t>27,73%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>46424</t>
+          <t>45453</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>60129</t>
+          <t>59901</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>54,59%</t>
+          <t>53,45%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>70,71%</t>
+          <t>70,44%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>55239</t>
+          <t>55911</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>71844</t>
+          <t>72022</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>58,23%</t>
+          <t>58,94%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>75,73%</t>
+          <t>75,92%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>106468</t>
+          <t>106098</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>128590</t>
+          <t>128132</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>59,18%</t>
+          <t>58,97%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>71,48%</t>
+          <t>71,22%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>24912</t>
+          <t>25140</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>38617</t>
+          <t>39588</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>29,29%</t>
+          <t>29,56%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>45,41%</t>
+          <t>46,55%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>23023</t>
+          <t>22845</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>39628</t>
+          <t>38956</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>24,27%</t>
+          <t>24,08%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>41,77%</t>
+          <t>41,06%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>51318</t>
+          <t>51776</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>73440</t>
+          <t>73810</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>28,52%</t>
+          <t>28,78%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>40,82%</t>
+          <t>41,03%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>236495</t>
+          <t>238447</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>272515</t>
+          <t>271852</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>71,64%</t>
+          <t>72,23%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>82,55%</t>
+          <t>82,35%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>261692</t>
+          <t>262850</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>296993</t>
+          <t>297538</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>67,77%</t>
+          <t>68,07%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>76,91%</t>
+          <t>77,05%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>510978</t>
+          <t>509862</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>561306</t>
+          <t>560684</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>71,34%</t>
+          <t>71,18%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>78,36%</t>
+          <t>78,28%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>57611</t>
+          <t>58274</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>93631</t>
+          <t>91679</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>17,65%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>28,36%</t>
+          <t>27,77%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>89156</t>
+          <t>88611</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>124457</t>
+          <t>123299</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>23,09%</t>
+          <t>22,95%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>32,23%</t>
+          <t>31,93%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>154969</t>
+          <t>155591</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>205297</t>
+          <t>206413</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>21,64%</t>
+          <t>21,72%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>28,66%</t>
+          <t>28,82%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/AIRE_1_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/AIRE_1_R-Estudios-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>25311</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>19218</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>28335</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>83,55%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>63,44%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>93,53%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>23958</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>19505</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>26653</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>84,38%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>68,7%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>93,88%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>27915</t>
+          <t>19183</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>22568</t>
+          <t>15063</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>31231</t>
+          <t>21823</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>84,46%</t>
+          <t>81,44%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>68,28%</t>
+          <t>63,95%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>94,49%</t>
+          <t>92,65%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>51872</t>
+          <t>44495</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>45420</t>
+          <t>38621</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>56317</t>
+          <t>48905</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>84,42%</t>
+          <t>82,63%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>73,92%</t>
+          <t>71,72%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>91,66%</t>
+          <t>90,82%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>4983</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>1959</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>11076</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>16,45%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>6,47%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>36,56%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>4433</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>1738</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>8886</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>15,62%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>6,12%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>31,3%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5137</t>
+          <t>4371</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1821</t>
+          <t>1731</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10484</t>
+          <t>8491</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>18,56%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>31,72%</t>
+          <t>36,05%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>9571</t>
+          <t>9354</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>5126</t>
+          <t>4944</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>16023</t>
+          <t>15228</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>17,37%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>26,08%</t>
+          <t>28,28%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>30294</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>30294</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>30294</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>28391</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>28391</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>28391</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>33052</t>
+          <t>23554</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>33052</t>
+          <t>23554</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>33052</t>
+          <t>23554</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>61443</t>
+          <t>53849</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>61443</t>
+          <t>53849</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>61443</t>
+          <t>53849</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>255</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>175883</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>161565</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>188181</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>73,53%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>67,54%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>78,67%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>233</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>175045</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>163444</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>188495</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>80,78%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>75,43%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>86,99%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>255</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>189772</t>
+          <t>149014</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>173960</t>
+          <t>139057</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>203403</t>
+          <t>158557</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>73,49%</t>
+          <t>77,92%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>67,37%</t>
+          <t>72,71%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>78,77%</t>
+          <t>82,91%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>364817</t>
+          <t>324897</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>343213</t>
+          <t>307430</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>387791</t>
+          <t>339203</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>76,82%</t>
+          <t>75,48%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>72,27%</t>
+          <t>71,42%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>81,65%</t>
+          <t>78,8%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>63327</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>51029</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>77645</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>26,47%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>21,33%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>32,46%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>65</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>41649</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>28199</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>53250</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>19,22%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>13,01%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>24,57%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>68458</t>
+          <t>42229</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>54827</t>
+          <t>32686</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>84270</t>
+          <t>52186</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>26,51%</t>
+          <t>22,08%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>21,23%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>32,63%</t>
+          <t>27,29%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>110106</t>
+          <t>105556</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>87132</t>
+          <t>91250</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>131710</t>
+          <t>123023</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>23,18%</t>
+          <t>24,52%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
+          <t>21,2%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>27,73%</t>
+          <t>28,58%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>345</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>239210</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>239210</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>239210</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>298</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>216694</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>216694</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>216694</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>345</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>258230</t>
+          <t>191243</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>258230</t>
+          <t>191243</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>258230</t>
+          <t>191243</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>474923</t>
+          <t>430453</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>474923</t>
+          <t>430453</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>474923</t>
+          <t>430453</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,107 +1406,107 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>59544</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>52084</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>66995</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>67,31%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>58,88%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>75,73%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>83</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>53255</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>45453</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>59901</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>62,62%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>53,45%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>53003</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>45656</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>60535</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>62,01%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>53,41%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>70,82%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>163</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>112546</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>102136</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>122513</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>64,71%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>58,72%</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
         <is>
           <t>70,44%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>64003</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>55911</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>72022</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>67,47%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>58,94%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>75,92%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>163</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>117258</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>106098</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>128132</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>65,18%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>58,97%</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>71,22%</t>
         </is>
       </c>
     </row>
@@ -1519,107 +1519,107 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>28916</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>21465</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>36376</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>32,69%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>24,27%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>41,12%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>50</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>31786</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>25140</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>39588</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>37,38%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>32472</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>24940</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>39819</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>37,99%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>29,18%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>46,59%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>61389</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>51422</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>71799</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>35,29%</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>29,56%</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>46,55%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>30864</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>22845</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>38956</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>32,53%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>24,08%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>41,06%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>62650</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>51776</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>73810</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>34,82%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>28,78%</t>
-        </is>
-      </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>41,03%</t>
+          <t>41,28%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>88460</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>88460</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>88460</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>133</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>85041</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>85041</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>85041</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>124</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>94867</t>
+          <t>85475</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>94867</t>
+          <t>85475</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>94867</t>
+          <t>85475</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>179908</t>
+          <t>173935</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>179908</t>
+          <t>173935</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>179908</t>
+          <t>173935</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,72 +1749,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>372</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>260739</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>244156</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>275967</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>72,84%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>68,21%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>77,09%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>345</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>252258</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>238447</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>271852</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>76,41%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>72,23%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>82,35%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>372</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>281689</t>
+          <t>221199</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>262850</t>
+          <t>208351</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>297538</t>
+          <t>233665</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>72,95%</t>
+          <t>73,67%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>68,07%</t>
+          <t>69,39%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>77,05%</t>
+          <t>77,82%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>533947</t>
+          <t>481939</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>509862</t>
+          <t>460074</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>560684</t>
+          <t>501237</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>74,55%</t>
+          <t>73,22%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>71,18%</t>
+          <t>69,89%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>78,28%</t>
+          <t>76,15%</t>
         </is>
       </c>
     </row>
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>97226</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>81998</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>113809</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>27,16%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>22,91%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>31,79%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>122</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>77868</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>58274</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>91679</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>23,59%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>17,65%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>27,77%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>139</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>104460</t>
+          <t>79073</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>88611</t>
+          <t>66607</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>123299</t>
+          <t>91921</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>27,05%</t>
+          <t>26,33%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>22,95%</t>
+          <t>22,18%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>31,93%</t>
+          <t>30,61%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>182328</t>
+          <t>176298</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>155591</t>
+          <t>157000</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>206413</t>
+          <t>198163</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>25,45%</t>
+          <t>26,78%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>21,72%</t>
+          <t>23,85%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>28,82%</t>
+          <t>30,11%</t>
         </is>
       </c>
     </row>
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>511</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>357965</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>357965</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>357965</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>467</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>330126</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>330126</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>330126</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>511</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>386149</t>
+          <t>300272</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>386149</t>
+          <t>300272</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>386149</t>
+          <t>300272</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>716275</t>
+          <t>658237</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>716275</t>
+          <t>658237</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>716275</t>
+          <t>658237</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
